--- a/数值校对_单回合伤害.xlsx
+++ b/数值校对_单回合伤害.xlsx
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1458,7 +1458,7 @@
         <v/>
       </c>
       <c r="AN2" s="6">
-        <f>1+IF(AD2=1,AE2,0)/100+AF2*'参数'!$B$15/100+AG2/100</f>
+        <f>1+IF(AD2=1,AE2+AF2*'参数'!$B$15+AG2,0)/100</f>
         <v/>
       </c>
       <c r="AO2" s="6">
@@ -1617,7 +1617,7 @@
         <v/>
       </c>
       <c r="AN3" s="6">
-        <f>1+IF(AD3=1,AE3,0)/100+AF3*'参数'!$B$15/100+AG3/100</f>
+        <f>1+IF(AD3=1,AE3+AF3*'参数'!$B$15+AG3,0)/100</f>
         <v/>
       </c>
       <c r="AO3" s="6">
@@ -1720,7 +1720,7 @@
         <v/>
       </c>
       <c r="Y4" s="10" t="n">
-        <v>232.8</v>
+        <v>226.8</v>
       </c>
       <c r="Z4" s="6">
         <f>'参数'!$B$7</f>
@@ -1775,7 +1775,7 @@
         <v/>
       </c>
       <c r="AN4" s="6">
-        <f>1+IF(AD4=1,AE4,0)/100+AF4*'参数'!$B$15/100+AG4/100</f>
+        <f>1+IF(AD4=1,AE4+AF4*'参数'!$B$15+AG4,0)/100</f>
         <v/>
       </c>
       <c r="AO4" s="6">
@@ -1878,7 +1878,7 @@
         <v/>
       </c>
       <c r="Y5" s="10" t="n">
-        <v>232.8</v>
+        <v>226.8</v>
       </c>
       <c r="Z5" s="6">
         <f>'参数'!$B$7</f>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="AN5" s="6">
-        <f>1+IF(AD5=1,AE5,0)/100+AF5*'参数'!$B$15/100+AG5/100</f>
+        <f>1+IF(AD5=1,AE5+AF5*'参数'!$B$15+AG5,0)/100</f>
         <v/>
       </c>
       <c r="AO5" s="6">
@@ -2093,7 +2093,7 @@
         <v/>
       </c>
       <c r="AN6" s="6">
-        <f>1+IF(AD6=1,AE6,0)/100+AF6*'参数'!$B$15/100+AG6/100</f>
+        <f>1+IF(AD6=1,AE6+AF6*'参数'!$B$15+AG6,0)/100</f>
         <v/>
       </c>
       <c r="AO6" s="6">
@@ -2252,7 +2252,7 @@
         <v/>
       </c>
       <c r="AN7" s="6">
-        <f>1+IF(AD7=1,AE7,0)/100+AF7*'参数'!$B$15/100+AG7/100</f>
+        <f>1+IF(AD7=1,AE7+AF7*'参数'!$B$15+AG7,0)/100</f>
         <v/>
       </c>
       <c r="AO7" s="6">
@@ -2411,7 +2411,7 @@
         <v/>
       </c>
       <c r="AN8" s="6">
-        <f>1+IF(AD8=1,AE8,0)/100+AF8*'参数'!$B$15/100+AG8/100</f>
+        <f>1+IF(AD8=1,AE8+AF8*'参数'!$B$15+AG8,0)/100</f>
         <v/>
       </c>
       <c r="AO8" s="6">
@@ -2571,7 +2571,7 @@
         <v/>
       </c>
       <c r="AN9" s="6">
-        <f>1+IF(AD9=1,AE9,0)/100+AF9*'参数'!$B$15/100+AG9/100</f>
+        <f>1+IF(AD9=1,AE9+AF9*'参数'!$B$15+AG9,0)/100</f>
         <v/>
       </c>
       <c r="AO9" s="6">
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="AN10" s="6">
-        <f>1+IF(AD10=1,AE10,0)/100+AF10*'参数'!$B$15/100+AG10/100</f>
+        <f>1+IF(AD10=1,AE10+AF10*'参数'!$B$15+AG10,0)/100</f>
         <v/>
       </c>
       <c r="AO10" s="6">
@@ -2890,7 +2890,7 @@
         <v/>
       </c>
       <c r="AN11" s="6">
-        <f>1+IF(AD11=1,AE11,0)/100+AF11*'参数'!$B$15/100+AG11/100</f>
+        <f>1+IF(AD11=1,AE11+AF11*'参数'!$B$15+AG11,0)/100</f>
         <v/>
       </c>
       <c r="AO11" s="6">
@@ -3049,7 +3049,7 @@
         <v/>
       </c>
       <c r="AN12" s="6">
-        <f>1+IF(AD12=1,AE12,0)/100+AF12*'参数'!$B$15/100+AG12/100</f>
+        <f>1+IF(AD12=1,AE12+AF12*'参数'!$B$15+AG12,0)/100</f>
         <v/>
       </c>
       <c r="AO12" s="6">
@@ -3208,7 +3208,7 @@
         <v/>
       </c>
       <c r="AN13" s="6">
-        <f>1+IF(AD13=1,AE13,0)/100+AF13*'参数'!$B$15/100+AG13/100</f>
+        <f>1+IF(AD13=1,AE13+AF13*'参数'!$B$15+AG13,0)/100</f>
         <v/>
       </c>
       <c r="AO13" s="6">
@@ -3367,7 +3367,7 @@
         <v/>
       </c>
       <c r="AN14" s="6">
-        <f>1+IF(AD14=1,AE14,0)/100+AF14*'参数'!$B$15/100+AG14/100</f>
+        <f>1+IF(AD14=1,AE14+AF14*'参数'!$B$15+AG14,0)/100</f>
         <v/>
       </c>
       <c r="AO14" s="6">
@@ -3526,7 +3526,7 @@
         <v/>
       </c>
       <c r="AN15" s="6">
-        <f>1+IF(AD15=1,AE15,0)/100+AF15*'参数'!$B$15/100+AG15/100</f>
+        <f>1+IF(AD15=1,AE15+AF15*'参数'!$B$15+AG15,0)/100</f>
         <v/>
       </c>
       <c r="AO15" s="6">
@@ -3685,7 +3685,7 @@
         <v/>
       </c>
       <c r="AN16" s="6">
-        <f>1+IF(AD16=1,AE16,0)/100+AF16*'参数'!$B$15/100+AG16/100</f>
+        <f>1+IF(AD16=1,AE16+AF16*'参数'!$B$15+AG16,0)/100</f>
         <v/>
       </c>
       <c r="AO16" s="6">
@@ -3844,7 +3844,7 @@
         <v/>
       </c>
       <c r="AN17" s="6">
-        <f>1+IF(AD17=1,AE17,0)/100+AF17*'参数'!$B$15/100+AG17/100</f>
+        <f>1+IF(AD17=1,AE17+AF17*'参数'!$B$15+AG17,0)/100</f>
         <v/>
       </c>
       <c r="AO17" s="6">
@@ -4004,7 +4004,7 @@
         <v/>
       </c>
       <c r="AN18" s="6">
-        <f>1+IF(AD18=1,AE18,0)/100+AF18*'参数'!$B$15/100+AG18/100</f>
+        <f>1+IF(AD18=1,AE18+AF18*'参数'!$B$15+AG18,0)/100</f>
         <v/>
       </c>
       <c r="AO18" s="6">
@@ -4163,7 +4163,7 @@
         <v/>
       </c>
       <c r="AN19" s="6">
-        <f>1+IF(AD19=1,AE19,0)/100+AF19*'参数'!$B$15/100+AG19/100</f>
+        <f>1+IF(AD19=1,AE19+AF19*'参数'!$B$15+AG19,0)/100</f>
         <v/>
       </c>
       <c r="AO19" s="6">
@@ -4186,7 +4186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -4256,7 +4256,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>7. 克制项 = 1 + 是否克制×基础克制系数/100 + 灵犀层数×灵犀每层/100 + 其他克制/100。</t>
+          <t>7. 克制项 = 1 + 是否克制×(基础克制系数+灵犀层数×灵犀每层+其他克制)/100；不克制时灵犀不生效。</t>
         </is>
       </c>
     </row>
@@ -4288,6 +4288,10 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/数值校对_单回合伤害.xlsx
+++ b/数值校对_单回合伤害.xlsx
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP19"/>
+  <dimension ref="A1:AS19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1310,6 +1310,21 @@
           <t>伤害</t>
         </is>
       </c>
+      <c r="AQ1" s="5" t="inlineStr">
+        <is>
+          <t>独白层数</t>
+        </is>
+      </c>
+      <c r="AR1" s="5" t="inlineStr">
+        <is>
+          <t>群像层数</t>
+        </is>
+      </c>
+      <c r="AS1" s="5" t="inlineStr">
+        <is>
+          <t>礼仪层数(仅仪式)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1469,6 +1484,15 @@
         <f>IF(C2=0,0,FLOOR(D2/100*AJ2*AK2*AL2*AM2*AN2*AO2,1))</f>
         <v/>
       </c>
+      <c r="AQ2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1628,6 +1652,15 @@
         <f>IF(C3=0,0,FLOOR(D3/100*AJ3*AK3*AL3*AM3*AN3*AO3,1))</f>
         <v/>
       </c>
+      <c r="AQ3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1643,8 +1676,9 @@
       <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2150</v>
+      <c r="D4" s="4">
+        <f>IF(ISNUMBER(SEARCH("全体",$B4)),1300+$AR4*70,1300+$AQ4*140)</f>
+        <v/>
       </c>
       <c r="E4" s="4" t="n">
         <v>1</v>
@@ -1734,7 +1768,7 @@
         <v/>
       </c>
       <c r="AC4" s="10" t="n">
-        <v>168</v>
+        <v>424.4</v>
       </c>
       <c r="AD4" s="4" t="n">
         <v>0</v>
@@ -1786,6 +1820,15 @@
         <f>IF(C4=0,0,FLOOR(D4/100*AJ4*AK4*AL4*AM4*AN4*AO4,1))</f>
         <v/>
       </c>
+      <c r="AQ4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1801,8 +1844,9 @@
       <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>2650</v>
+      <c r="D5" s="4">
+        <f>IF(ISNUMBER(SEARCH("全体",$B5)),1300+$AR5*70,1300+$AQ5*140)</f>
+        <v/>
       </c>
       <c r="E5" s="4" t="n">
         <v>1</v>
@@ -1892,7 +1936,7 @@
         <v/>
       </c>
       <c r="AC5" s="10" t="n">
-        <v>168</v>
+        <v>424.4</v>
       </c>
       <c r="AD5" s="4" t="n">
         <v>0</v>
@@ -1944,6 +1988,15 @@
         <f>IF(C5=0,0,FLOOR(D5/100*AJ5*AK5*AL5*AM5*AN5*AO5,1))</f>
         <v/>
       </c>
+      <c r="AQ5" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2104,6 +2157,15 @@
         <f>IF(C6=0,0,FLOOR(D6/100*AJ6*AK6*AL6*AM6*AN6*AO6,1))</f>
         <v/>
       </c>
+      <c r="AQ6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -2263,6 +2325,15 @@
         <f>IF(C7=0,0,FLOOR(D7/100*AJ7*AK7*AL7*AM7*AN7*AO7,1))</f>
         <v/>
       </c>
+      <c r="AQ7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2422,6 +2493,15 @@
         <f>IF(C8=0,0,FLOOR(D8/100*AJ8*AK8*AL8*AM8*AN8*AO8,1))</f>
         <v/>
       </c>
+      <c r="AQ8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2582,6 +2662,15 @@
         <f>IF(C9=0,0,FLOOR(D9/100*AJ9*AK9*AL9*AM9*AN9*AO9,1))</f>
         <v/>
       </c>
+      <c r="AQ9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2742,6 +2831,15 @@
         <f>IF(C10=0,0,FLOOR(D10/100*AJ10*AK10*AL10*AM10*AN10*AO10,1))</f>
         <v/>
       </c>
+      <c r="AQ10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2901,6 +2999,15 @@
         <f>IF(C11=0,0,FLOOR(D11/100*AJ11*AK11*AL11*AM11*AN11*AO11,1))</f>
         <v/>
       </c>
+      <c r="AQ11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3060,6 +3167,15 @@
         <f>IF(C12=0,0,FLOOR(D12/100*AJ12*AK12*AL12*AM12*AN12*AO12,1))</f>
         <v/>
       </c>
+      <c r="AQ12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3219,6 +3335,15 @@
         <f>IF(C13=0,0,FLOOR(D13/100*AJ13*AK13*AL13*AM13*AN13*AO13,1))</f>
         <v/>
       </c>
+      <c r="AQ13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3378,6 +3503,15 @@
         <f>IF(C14=0,0,FLOOR(D14/100*AJ14*AK14*AL14*AM14*AN14*AO14,1))</f>
         <v/>
       </c>
+      <c r="AQ14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3537,6 +3671,15 @@
         <f>IF(C15=0,0,FLOOR(D15/100*AJ15*AK15*AL15*AM15*AN15*AO15,1))</f>
         <v/>
       </c>
+      <c r="AQ15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3696,6 +3839,15 @@
         <f>IF(C16=0,0,FLOOR(D16/100*AJ16*AK16*AL16*AM16*AN16*AO16,1))</f>
         <v/>
       </c>
+      <c r="AQ16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3855,6 +4007,15 @@
         <f>IF(C17=0,0,FLOOR(D17/100*AJ17*AK17*AL17*AM17*AN17*AO17,1))</f>
         <v/>
       </c>
+      <c r="AQ17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4015,6 +4176,15 @@
         <f>IF(C18=0,0,FLOOR(D18/100*AJ18*AK18*AL18*AM18*AN18*AO18,1))</f>
         <v/>
       </c>
+      <c r="AQ18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4173,6 +4343,15 @@
       <c r="AP19" s="6">
         <f>IF(C19=0,0,FLOOR(D19/100*AJ19*AK19*AL19*AM19*AN19*AO19,1))</f>
         <v/>
+      </c>
+      <c r="AQ19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4186,7 +4365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -4277,7 +4456,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>10. 战备层数会在仪式行动中自动引用“参数”表的莫莉德尔战备层数；反击创伤% 会自动只对反击类行动生效。</t>
+          <t>10. 虚构集大招倍率按“群像只进AOE、独白只进主目标”自动计算，独白/群像层数填写在AQ/AR列。</t>
         </is>
       </c>
     </row>
@@ -4292,6 +4471,8 @@
     <row r="16"/>
     <row r="17"/>
     <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/数值校对_单回合伤害.xlsx
+++ b/数值校对_单回合伤害.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -612,8 +612,9 @@
           <t>灵犀层数</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>5</v>
+      <c r="B14" s="6">
+        <f>IF('参数'!$B$41&gt;=5,10,IF('参数'!$B$41&gt;=2,7,5))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -622,8 +623,9 @@
           <t>灵犀每层克制 %</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>4</v>
+      <c r="B15" s="6">
+        <f>IF('参数'!$B$41&gt;=2,5,4)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -649,8 +651,9 @@
           <t>加护创伤加成 %</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>30</v>
+      <c r="B18" s="6">
+        <f>IF('参数'!$B$41&gt;=3,20,15)+MIN(IF('参数'!$B$41&gt;=3,21,15),$B$14*3)</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -686,8 +689,9 @@
           <t>群鸟之歌术法威力 %</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>30</v>
+      <c r="B22" s="6">
+        <f>IF('参数'!$B$41&gt;=1,45,30)</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -696,8 +700,9 @@
           <t>群鸟之歌仪式威力 %</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>30</v>
+      <c r="B23" s="6">
+        <f>IF('参数'!$B$41&gt;=1,45,30)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -835,6 +840,46 @@
       </c>
       <c r="B38" s="10" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>虚构集塑造</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>小瑞安侬塑造</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>莫莉德尔塑造</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>J塑造</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1389,8 +1434,9 @@
       <c r="Q2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="4" t="n">
-        <v>2</v>
+      <c r="R2" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S2" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B2)),$B2="高温回火"),'参数'!$B$20,0)</f>
@@ -1557,8 +1603,9 @@
       <c r="Q3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R3" s="4" t="n">
-        <v>2</v>
+      <c r="R3" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S3" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B3)),$B3="高温回火"),'参数'!$B$20,0)</f>
@@ -1677,7 +1724,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>IF(ISNUMBER(SEARCH("全体",$B4)),1300+$AR4*70,1300+$AQ4*140)</f>
+        <f>IF(ISNUMBER(SEARCH("全体",$B4)),2*IF('参数'!$B$40&gt;=5,650,IF('参数'!$B$40&gt;=3,550,450))+$AR4*(2*IF('参数'!$B$40&gt;=2,35,25)),2*IF('参数'!$B$40&gt;=5,650,IF('参数'!$B$40&gt;=3,550,450))+$AQ4*(2*IF('参数'!$B$40&gt;=2,70,50)))</f>
         <v/>
       </c>
       <c r="E4" s="4" t="n">
@@ -1727,8 +1774,9 @@
         <f>IF($AA4=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R4" s="4" t="n">
-        <v>2</v>
+      <c r="R4" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S4" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B4)),$B4="高温回火"),'参数'!$B$20,0)</f>
@@ -1845,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>IF(ISNUMBER(SEARCH("全体",$B5)),1300+$AR5*70,1300+$AQ5*140)</f>
+        <f>IF(ISNUMBER(SEARCH("全体",$B5)),2*IF('参数'!$B$40&gt;=5,650,IF('参数'!$B$40&gt;=3,550,450))+$AR5*(2*IF('参数'!$B$40&gt;=2,35,25)),2*IF('参数'!$B$40&gt;=5,650,IF('参数'!$B$40&gt;=3,550,450))+$AQ5*(2*IF('参数'!$B$40&gt;=2,70,50)))</f>
         <v/>
       </c>
       <c r="E5" s="4" t="n">
@@ -1895,8 +1943,9 @@
         <f>IF($AA5=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>2</v>
+      <c r="R5" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S5" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B5)),$B5="高温回火"),'参数'!$B$20,0)</f>
@@ -2062,8 +2111,9 @@
         <f>IF($AA6=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>2</v>
+      <c r="R6" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S6" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B6)),$B6="高温回火"),'参数'!$B$20,0)</f>
@@ -2230,8 +2280,9 @@
       <c r="Q7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>2</v>
+      <c r="R7" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S7" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B7)),$B7="高温回火"),'参数'!$B$20,0)</f>
@@ -2398,8 +2449,9 @@
       <c r="Q8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="4" t="n">
-        <v>2</v>
+      <c r="R8" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S8" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B8)),$B8="高温回火"),'参数'!$B$20,0)</f>
@@ -2567,8 +2619,9 @@
         <f>IF($AA9=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R9" s="4" t="n">
-        <v>2</v>
+      <c r="R9" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S9" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B9)),$B9="高温回火"),'参数'!$B$20,0)</f>
@@ -2736,8 +2789,9 @@
         <f>IF($AA10=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R10" s="4" t="n">
-        <v>2</v>
+      <c r="R10" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S10" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B10)),$B10="高温回火"),'参数'!$B$20,0)</f>
@@ -2904,8 +2958,9 @@
       <c r="Q11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R11" s="4" t="n">
-        <v>2</v>
+      <c r="R11" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S11" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B11)),$B11="高温回火"),'参数'!$B$20,0)</f>
@@ -3072,8 +3127,9 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>2</v>
+      <c r="R12" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S12" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B12)),$B12="高温回火"),'参数'!$B$20,0)</f>
@@ -3240,8 +3296,9 @@
       <c r="Q13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="4" t="n">
-        <v>2</v>
+      <c r="R13" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S13" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B13)),$B13="高温回火"),'参数'!$B$20,0)</f>
@@ -3408,8 +3465,9 @@
       <c r="Q14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="4" t="n">
-        <v>2</v>
+      <c r="R14" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S14" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B14)),$B14="高温回火"),'参数'!$B$20,0)</f>
@@ -3576,8 +3634,9 @@
       <c r="Q15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="4" t="n">
-        <v>2</v>
+      <c r="R15" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S15" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B15)),$B15="高温回火"),'参数'!$B$20,0)</f>
@@ -3744,8 +3803,9 @@
       <c r="Q16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R16" s="4" t="n">
-        <v>2</v>
+      <c r="R16" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S16" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B16)),$B16="高温回火"),'参数'!$B$20,0)</f>
@@ -3912,8 +3972,9 @@
       <c r="Q17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R17" s="4" t="n">
-        <v>2</v>
+      <c r="R17" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S17" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B17)),$B17="高温回火"),'参数'!$B$20,0)</f>
@@ -4081,8 +4142,9 @@
         <f>IF($AA18=2,'参数'!$B$32,0)</f>
         <v/>
       </c>
-      <c r="R18" s="4" t="n">
-        <v>2</v>
+      <c r="R18" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S18" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B18)),$B18="高温回火"),'参数'!$B$20,0)</f>
@@ -4249,8 +4311,9 @@
       <c r="Q19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R19" s="4" t="n">
-        <v>2</v>
+      <c r="R19" s="4">
+        <f>IF('参数'!$B$42&gt;=2,2.5,2)</f>
+        <v/>
       </c>
       <c r="S19" s="6">
         <f>IF(OR(ISNUMBER(SEARCH("反击",$B19)),$B19="高温回火"),'参数'!$B$20,0)</f>
@@ -4365,7 +4428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -4463,7 +4526,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>11. 暴击创伤% 会自动加上“昨日雨声轻暴击创伤”和“家庭指导员暴击创伤”。</t>
+          <t>11. 塑造选择在“参数”表底部；角色属性表中的面板数值需手动按对应塑造填写。</t>
         </is>
       </c>
     </row>
@@ -4473,6 +4536,10 @@
     <row r="18"/>
     <row r="19"/>
     <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
